--- a/input/base_kg_sample.xlsx
+++ b/input/base_kg_sample.xlsx
@@ -125,13 +125,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_base_kg" displayName="_base_kg" ref="A1:B4" headerRowCount="1">
-  <autoFilter ref="A1:B4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="_base_kg" displayName="_base_kg" ref="A1:B174" headerRowCount="1">
+  <autoFilter ref="A1:B174"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Наименование, регион"/>
     <tableColumn id="2" name="Компании группы (ЕРЗ)"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -424,8 +424,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -472,6 +476,2046 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>АО ЗемПроектСтрой (ИНН 1000000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ПИК, г.Москва</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>АО ПИК Строй (ИНН 1000000000); ООО ПИК Девелопмент (ИНН 1000000001); ПАО ПИК Инвест (ИНН 1000000002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Холдинг Setl Group, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ООО Setl Group (ИНН 2000000010), АО Setl Group Капитал (ИНН 2000000011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Группа ЛСР, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>АО ЛСР (ИНН 3000000002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ГК Самолет, г.Москва</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); ООО Самолет Сервис (ИНН 4000000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Фонд реновации, г.Москва</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО реновации Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ГК ЮгСтройИнвест, Ставропольский край</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>АО ЮгСтройИнвест (ИНН 5000000015); ООО ЮгСтройИнвест Девелопмент (ИНН 5000000016), СЗ ЮгСтройИнвест Проект (ИНН 5000000017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ГК ФСК, г.Москва</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>АО ФСК Проект (ИНН 6000000060); ООО ФСК ЖБИ (ИНН 6000000061); ПАО ФСК Сервис (ИНН 6000000062); ЗАО ФСК Трейд (ИНН 6000000063)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Эталон, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>АО Эталон Риэлт (ИНН 5001000004); ООО Эталон (ИНН 7801000005); ЗАО Эталон Инвест (ИНН 7000000007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>А101 ДЕВЕЛОПМЕНТ, г.Москва</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>АО А101 ДЕВЕЛОПМЕНТ (ИНН 8000000001); ООО А101 ДЕВЕЛОПМЕНТ Трейд (ИНН 8000000001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ГК Гранель, г.Москва</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО Гранель Регион (ИНН 9000000045); ООО Гранель Сити (ИНН 9000000046)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Группа ЦДС, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>АО ЦДС Строй (ИНН 1000000100); ООО ЦДС Девелопмент (ИНН 1000000101); ПАО ЦДС Инвест (ИНН 1000000102)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Объединение застройщиков ВКБ-Новостройки, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ООО застройщиков ВКБ (ИНН 2000000110), АО застройщиков ВКБ Капитал (ИНН 2000000111)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ДОНСТРОЙ, г.Москва</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>АО ДОНСТРОЙ (ИНН 3000000012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ДСК, Воронежская область</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>АО Новый ЖБИ (ИНН 7701000001); ООО ДСК Сервис (ИНН 4000000013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ГК КОРТРОС, г.Москва</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО КОРТРОС Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>MR Group, г.Москва</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>АО MR Group (ИНН 5000000045); ООО MR Group Девелопмент (ИНН 5000000046), СЗ MR Group Проект (ИНН 5000000047)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ГК ИНГРАД (Sminex), г.Москва</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>АО ИНГРАД (Sminex) Сити (ИНН 6000000160); ООО ИНГРАД (Sminex) Регион (ИНН 6000000161); ПАО ИНГРАД (Sminex) Строй (ИНН 6000000162); ЗАО ИНГРАД (Sminex) Девелопмент (ИНН 6000000163)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Брусника, Свердловская область</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>АО Брусника Риэлт (ИНН 5001000004); ООО Брусника (ИНН 7801000005); ЗАО Брусника Инвест (ИНН 7000000017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>КП УГС, г.Москва</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>АО КП УГС (ИНН 8000000003); ООО КП УГС Трейд (ИНН 8000000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DOGMA, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО DOGMA Регион (ИНН 9000000095); ООО DOGMA Сити (ИНН 9000000096)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ГК МИЦ, г.Москва</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>АО МИЦ Строй (ИНН 1000000200); ООО МИЦ Девелопмент (ИНН 1000000201); ПАО МИЦ Инвест (ИНН 1000000202)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ГК Главстрой, г.Москва</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ООО Главстрой (ИНН 2000000210), АО Главстрой Капитал (ИНН 2000000211)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Унистрой, Республика Татарстан (Татарстан)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>АО Унистрой (ИНН 3000000022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>СК ВЫБОР, Воронежская область</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ООО ЖБИ-23 Трейд (ИНН 7701000001); ООО СК ВЫБОР Сервис (ИНН 4000000023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ГК ССК, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО ССК Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ГК Единство, Рязанская область</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>АО Единство (ИНН 5000000075); ООО Единство Девелопмент (ИНН 5000000076), СЗ Единство Проект (ИНН 5000000077)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Полис Групп, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>АО Полис Групп Сервис (ИНН 6000000260); ООО Полис Групп Трейд (ИНН 6000000261); ПАО Полис Групп Логистик (ИНН 6000000262); ЗАО Полис Групп Недвижимость (ИНН 6000000263)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ГК АБСОЛЮТ, г.Москва</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>АО АБСОЛЮТ Риэлт (ИНН 5001000004); ООО АБСОЛЮТ (ИНН 7801000005); ЗАО АБСОЛЮТ Инвест (ИНН 7000000027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Страна Девелопмент, Тюменская область</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>АО Страна Девелопмент (ИНН 8000000005); ООО Страна Девелопмент Трейд (ИНН 8000000005)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Атомстройкомплекс, Свердловская область</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО Атомстройкомплекс Регион (ИНН 9000000145); ООО Атомстройкомплекс Сити (ИНН 9000000146)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ГК ИНСИТИ девелопмент, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>АО ИНСИТИ девелопмент Строй (ИНН 1000000300); ООО ИНСИТИ девелопмент Девелопмент (ИНН 1000000301); ПАО ИНСИТИ девелопмент Инвест (ИНН 1000000302)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>КОМОССТРОЙ®, Удмуртская Республика</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ООО КОМОССТРОЙ® (ИНН 2000000310), АО КОМОССТРОЙ® Капитал (ИНН 2000000311)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Лидер Групп, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>АО Лидер Групп (ИНН 3000000032)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Сибпромстрой, Московская область</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); ООО Сибпромстрой Сервис (ИНН 4000000033)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ГК Пионер, г.Москва</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО Пионер Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ФСК Лидер, г.Москва</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>АО ФСК Лидер (ИНН 5000000105); ООО ФСК Лидер Девелопмент (ИНН 5000000106), СЗ ФСК Лидер Проект (ИНН 5000000107)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Группа Самолет-Девелопмент, г.Москва</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>АО Самолет Девелопмент Строй (ИНН 6000000360); ООО Самолет Девелопмент Девелопмент (ИНН 6000000361); ПАО Самолет Девелопмент Инвест (ИНН 6000000362); ЗАО Самолет Девелопмент Холдинг (ИНН 6000000363)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ГК КВС, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>АО КВС Риэлт (ИНН 5001000004); ООО КВС (ИНН 7801000005); ЗАО КВС Инвест (ИНН 7000000037)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ГК Томская ДСК, Томская область</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>АО Томская ДСК (ИНН 8000000007); ООО Томская ДСК Трейд (ИНН 8000000007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Концерн ЮИТ, г.Москва</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО Концерн ЮИТ Регион (ИНН 9000000195); ООО Концерн ЮИТ Сити (ИНН 9000000196)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>СЗ Резиденс, г.Москва</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>АО СЗ Резиденс Строй (ИНН 1000000400); ООО СЗ Резиденс Девелопмент (ИНН 1000000401); ПАО СЗ Резиденс Инвест (ИНН 1000000402)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Трест Спецкаучукремстрой, Республика Татарстан (Татарстан)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ООО Трест Спецкаучукремстрой (ИНН 2000000410), АО Трест Спецкаучукремстрой Капитал (ИНН 2000000411)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ПМК-5, Республика Марий Эл</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>АО ПМК (ИНН 3000000042)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>СК ПГС, Республика Бурятия</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>АО Новый ЖБИ (ИНН 7701000001); ООО СК ПГС Сервис (ИНН 4000000043)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ГК SUN DEVELOPMENT, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО SUN DEVELOPMENT Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ГК PRIME GROUP, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>АО PRIME GROUP (ИНН 5000000135); ООО PRIME GROUP Девелопмент (ИНН 5000000136), СЗ PRIME GROUP Проект (ИНН 5000000137)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>КМЗ Александрия, Московская область</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>АО КМЗ Александрия Логистик (ИНН 6000000460); ООО КМЗ Александрия Недвижимость (ИНН 6000000461); ПАО КМЗ Александрия Риэлт (ИНН 6000000462); ЗАО КМЗ Александрия Консалтинг (ИНН 6000000463)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>СК Магистр, Челябинская область</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>АО СК Магистр Риэлт (ИНН 5001000004); ООО СК Магистр (ИНН 7801000005); ЗАО СК Магистр Инвест (ИНН 7000000047)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>СО Арктика, Ямало-Ненецкий автономный округ</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>АО СО Арктика (ИНН 8000000009); ООО СО Арктика Трейд (ИНН 8000000009)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ФЗПГ ТО, Тульская область</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО ФЗПГ ТО Регион (ИНН 9000000245); ООО ФЗПГ ТО Сити (ИНН 9000000246)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>СЗ Мегагруп, Челябинская область</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>АО СЗ Мегагруп Строй (ИНН 1000000500); ООО СЗ Мегагруп Девелопмент (ИНН 1000000501); ПАО СЗ Мегагруп Инвест (ИНН 1000000502)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>НЭСК, Тульская область</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>ООО НЭСК (ИНН 2000000510), АО НЭСК Капитал (ИНН 2000000511)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ГК Базис, Челябинская область</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>АО Базис (ИНН 3000000052)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>ГК Апсис Глоб, г.Москва</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ООО ЖБИ-23 Трейд (ИНН 7701000001); ООО Апсис Глоб Сервис (ИНН 4000000053)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Эверест, Курганская область</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО Эверест Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>ГРОДНОВНЕШСТРОЙ, Калужская область</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>АО ГРОДНОВНЕШСТРОЙ (ИНН 5000000165); ООО ГРОДНОВНЕШСТРОЙ Девелопмент (ИНН 5000000166), СЗ ГРОДНОВНЕШСТРОЙ Проект (ИНН 5000000167)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>СЗ СтарСтрой+, Тамбовская область</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>АО СЗ СтарСтрой+ Инвест (ИНН 6000000560); ООО СЗ СтарСтрой+ Холдинг (ИНН 6000000561); ПАО СЗ СтарСтрой+ Групп (ИНН 6000000562); ЗАО СЗ СтарСтрой+ Капитал (ИНН 6000000563)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>СИК Кристалл, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>АО СИК Кристалл Риэлт (ИНН 5001000004); ООО СИК Кристалл (ИНН 7801000005); ЗАО СИК Кристалл Инвест (ИНН 7000000057)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>ОАО СПК Мосэнергострой, г.Москва</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>АО ОАО СПК (ИНН 8000000011); ООО ОАО СПК Трейд (ИНН 8000000011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>СК Воин-В, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО СК Воин Регион (ИНН 9000000295); ООО СК Воин Сити (ИНН 9000000296)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Альянс Вега Билдинг, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>АО Альянс Вега Строй (ИНН 1000000600); ООО Альянс Вега Девелопмент (ИНН 1000000601); ПАО Альянс Вега Инвест (ИНН 1000000602)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Газхолодмаш, Ямало-Ненецкий автономный округ</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>ООО Газхолодмаш (ИНН 2000000610), АО Газхолодмаш Капитал (ИНН 2000000611)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>ГК ВЕРСО М, г.Москва</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>АО ВЕРСО (ИНН 3000000062)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ПроектСервис-Юг, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); ООО ПроектСервис Юг Сервис (ИНН 4000000063)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>БВ СЗ, Волгоградская область</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО БВ СЗ Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Фирма СТЭН, Кировская область</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>АО Фирма СТЭН (ИНН 5000000195); ООО Фирма СТЭН Девелопмент (ИНН 5000000196), СЗ Фирма СТЭН Проект (ИНН 5000000197)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Оптима-Строй, Республика Саха (Якутия)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>АО Оптима Строй Риэлт (ИНН 6000000660); ООО Оптима Строй Консалтинг (ИНН 6000000661); ПАО Оптима Строй Парк (ИНН 6000000662); ЗАО Оптима Строй Центр (ИНН 6000000663)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ГК Форра, Самарская область</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>АО Форра Риэлт (ИНН 5001000004); ООО Форра (ИНН 7801000005); ЗАО Форра Инвест (ИНН 7000000067)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>СЗ Тройка Плюс, Московская область</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>АО СЗ Тройка (ИНН 8000000013); ООО СЗ Тройка Трейд (ИНН 8000000013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Атрус, Ярославская область</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО Атрус Регион (ИНН 9000000345); ООО Атрус Сити (ИНН 9000000346)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>СЗ КавказЭлитСтрой, Ставропольский край</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>АО СЗ КавказЭлитСтрой Строй (ИНН 1000000700); ООО СЗ КавказЭлитСтрой Девелопмент (ИНН 1000000701); ПАО СЗ КавказЭлитСтрой Инвест (ИНН 1000000702)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Группа компаний Строй-Акцент, Свердловская область</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ООО компаний Строй (ИНН 2000000710), АО компаний Строй Капитал (ИНН 2000000711)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Дементор, г.Севастополь</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>АО Дементор (ИНН 3000000072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>СЗ Метр2менеджмент, Астраханская область</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>АО Новый ЖБИ (ИНН 7701000001); ООО СЗ Метр2менеджмент Сервис (ИНН 4000000073)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>ООО МК 137, Республика Бурятия</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО ООО МК Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ЖК Аэропорт, Брянская область</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>АО ЖК Аэропорт (ИНН 5000000225); ООО ЖК Аэропорт Девелопмент (ИНН 5000000226), СЗ ЖК Аэропорт Проект (ИНН 5000000227)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>НовоСтрой, Ставропольский край</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>АО НовоСтрой Групп (ИНН 6000000760); ООО НовоСтрой Капитал (ИНН 6000000761); ПАО НовоСтрой Проект (ИНН 6000000762); ЗАО НовоСтрой ЖБИ (ИНН 6000000763)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Строительный трест №1, Ярославская область</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>АО Строительный трест Риэлт (ИНН 5001000004); ООО Строительный трест (ИНН 7801000005); ЗАО Строительный трест Инвест (ИНН 7000000077)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ХК Форум, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>АО ХК Форум (ИНН 8000000015); ООО ХК Форум Трейд (ИНН 8000000015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>ГлавУКС, Кемеровская область</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО ГлавУКС Регион (ИНН 9000000395); ООО ГлавУКС Сити (ИНН 9000000396)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>СЗ Пулковский, Иркутская область</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>АО СЗ Пулковский Строй (ИНН 1000000800); ООО СЗ Пулковский Девелопмент (ИНН 1000000801); ПАО СЗ Пулковский Инвест (ИНН 1000000802)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>СЗ Содружество, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>ООО СЗ Содружество (ИНН 2000000810), АО СЗ Содружество Капитал (ИНН 2000000811)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>ГК Мособлжилстрой Девелопмент, Московская область</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>АО Мособлжилстрой Девелопмент (ИНН 3000000082)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>БизнесПартнер, Ставропольский край</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ООО ЖБИ-23 Трейд (ИНН 7701000001); ООО БизнесПартнер Сервис (ИНН 4000000083)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Дедал-Сервиc, Волгоградская область</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО Дедал Сервиc Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>СЗ СМУ-2, Волгоградская область</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>АО СЗ СМУ (ИНН 5000000255); ООО СЗ СМУ Девелопмент (ИНН 5000000256), СЗ СЗ СМУ Проект (ИНН 5000000257)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ГК ТАК, Новосибирская область</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>АО ТАК Парк (ИНН 6000000860); ООО ТАК Центр (ИНН 6000000861); ПАО ТАК Сити (ИНН 6000000862); ЗАО ТАК Регион (ИНН 6000000863)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Проектно-Строительная фирма СТАР, Тюменская область</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>АО Проектно Строительная Риэлт (ИНН 5001000004); ООО Проектно Строительная (ИНН 7801000005); ЗАО Проектно Строительная Инвест (ИНН 7000000087)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ПМК-83, Республика Северная Осетия-Алания</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>АО ПМК 83 (ИНН 8000000017); ООО ПМК 83 Трейд (ИНН 8000000017)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>СЗ Эс Ай Эс Девелопмент, г.Москва</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО СЗ Эс Регион (ИНН 9000000445); ООО СЗ Эс Сити (ИНН 9000000446)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ГК Дортрансстрой, Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>АО Дортрансстрой Строй (ИНН 1000000900); ООО Дортрансстрой Девелопмент (ИНН 1000000901); ПАО Дортрансстрой Инвест (ИНН 1000000902)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>СЗ ИнвестСтрой, Свердловская область</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ООО СЗ ИнвестСтрой (ИНН 2000000910), АО СЗ ИнвестСтрой Капитал (ИНН 2000000911)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>НПФ БизнесСтрой, Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>АО НПФ БизнесСтрой (ИНН 3000000092)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Охта Групп, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); ООО Охта Групп Сервис (ИНН 4000000093)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>СЗ ОМЕГА-НВ, г.Севастополь</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СЗ ОМЕГА Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Холдинг Эко-Тепло, г.Москва</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>АО Эко Тепло (ИНН 5000000285); ООО Эко Тепло Девелопмент (ИНН 5000000286), СЗ Эко Тепло Проект (ИНН 5000000287)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ГК ИнвестСтрой, Калининградская область</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>АО ИнвестСтрой Проект (ИНН 6000000960); ООО ИнвестСтрой ЖБИ (ИНН 6000000961); ПАО ИнвестСтрой Сервис (ИНН 6000000962); ЗАО ИнвестСтрой Трейд (ИНН 6000000963)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Р-Фикс, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>АО Фикс Риэлт (ИНН 5001000004); ООО Фикс (ИНН 7801000005); ЗАО Фикс Инвест (ИНН 7000000097)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Альфа-Строй, Чувашская Республика-Чувашия</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>АО Альфа Строй (ИНН 8000000019); ООО Альфа Строй Трейд (ИНН 8000000019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ГК Корстон, Республика Татарстан (Татарстан)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО Корстон Регион (ИНН 9000000495); ООО Корстон Сити (ИНН 9000000496)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ГК Квадрат 27, Хабаровский край</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>АО Квадрат 27 Строй (ИНН 1000001000); ООО Квадрат 27 Девелопмент (ИНН 1000001001); ПАО Квадрат 27 Инвест (ИНН 1000001002)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>МаСт, Владимирская область</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ООО МаСт (ИНН 2000001010), АО МаСт Капитал (ИНН 2000001011)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Олимп, Липецкая область</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>АО Олимп (ИНН 3000000102)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Рецитал, Липецкая область</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>АО Новый ЖБИ (ИНН 7701000001); ООО Рецитал Сервис (ИНН 4000000103)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>СК Вира, Ленинградская область</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СК Вира Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Строй-Актив, Костромская область</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>АО Строй Актив (ИНН 5000000315); ООО Строй Актив Девелопмент (ИНН 5000000316), СЗ Строй Актив Проект (ИНН 5000000317)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>СЗ Возрождение, Тамбовская область</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>АО СЗ Возрождение Сити (ИНН 6000001060); ООО СЗ Возрождение Регион (ИНН 6000001061); ПАО СЗ Возрождение Строй (ИНН 6000001062); ЗАО СЗ Возрождение Девелопмент (ИНН 6000001063)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Группа Компаний СтоунСтрой, Тюменская область</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>АО Компаний СтоунСтрой Риэлт (ИНН 5001000004); ООО Компаний СтоунСтрой (ИНН 7801000005); ЗАО Компаний СтоунСтрой Инвест (ИНН 7000000107)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>СК Ренова, Республика Марий Эл</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>АО СК Ренова (ИНН 8000000021); ООО СК Ренова Трейд (ИНН 8000000021)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>СЗ РЕАЛ, Вологодская область</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО СЗ РЕАЛ Регион (ИНН 9000000545); ООО СЗ РЕАЛ Сити (ИНН 9000000546)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>СК ДОРС, Костромская область</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>АО СК ДОРС Строй (ИНН 1000001100); ООО СК ДОРС Девелопмент (ИНН 1000001101); ПАО СК ДОРС Инвест (ИНН 1000001102)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Концерн Покровский, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ООО Концерн Покровский (ИНН 2000001110), АО Концерн Покровский Капитал (ИНН 2000001111)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Вертикаль, Московская область</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>АО Вертикаль (ИНН 3000000112)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Монолит-Строй, Ямало-Ненецкий автономный округ</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>ООО ЖБИ-23 Трейд (ИНН 7701000001); ООО Монолит Строй Сервис (ИНН 4000000113)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>СК ДОМиК, Нижегородская область</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СК ДОМиК Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>СЗ Таврида, Томская область</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>АО СЗ Таврида (ИНН 5000000345); ООО СЗ Таврида Девелопмент (ИНН 5000000346), СЗ СЗ Таврида Проект (ИНН 5000000347)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>СЗ-58, Пензенская область</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>АО СЗ 58 Сервис (ИНН 6000001160); ООО СЗ 58 Трейд (ИНН 6000001161); ПАО СЗ 58 Логистик (ИНН 6000001162); ЗАО СЗ 58 Недвижимость (ИНН 6000001163)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ДСН-1, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>АО ДСН Риэлт (ИНН 5001000004); ООО ДСН (ИНН 7801000005); ЗАО ДСН Инвест (ИНН 7000000117)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>СЗ Файл, Пермский край</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>АО СЗ Файл (ИНН 8000000023); ООО СЗ Файл Трейд (ИНН 8000000023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>АС-ИНВЕСТ, Владимирская область</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО АС ИНВЕСТ Регион (ИНН 9000000595); ООО АС ИНВЕСТ Сити (ИНН 9000000596)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>СЗ Стройкомфорт, Владимирская область</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>АО СЗ Стройкомфорт Строй (ИНН 1000001200); ООО СЗ Стройкомфорт Девелопмент (ИНН 1000001201); ПАО СЗ Стройкомфорт Инвест (ИНН 1000001202)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Инвест проект, г.Москва</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>ООО Инвест проект (ИНН 2000001210), АО Инвест проект Капитал (ИНН 2000001211)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>СЗ Позитив, Ставропольский край</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>АО СЗ Позитив (ИНН 3000000122)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>СЗ Киносити Рыбинск, Ярославская область</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); ООО СЗ Киносити Сервис (ИНН 4000000123)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>СЗ Строитель-45, Курганская область</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СЗ Строитель Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ЮПС, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>АО ЮПС (ИНН 5000000375); ООО ЮПС Девелопмент (ИНН 5000000376), СЗ ЮПС Проект (ИНН 5000000377)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>УНИВЕРСАЛСТРОЙ, г.Санкт-Петербург</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>АО УНИВЕРСАЛСТРОЙ Строй (ИНН 6000001260); ООО УНИВЕРСАЛСТРОЙ Девелопмент (ИНН 6000001261); ПАО УНИВЕРСАЛСТРОЙ Инвест (ИНН 6000001262); ЗАО УНИВЕРСАЛСТРОЙ Холдинг (ИНН 6000001263)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>СаратоврегионстройС, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>АО СаратоврегионстройС Риэлт (ИНН 5001000004); ООО СаратоврегионстройС (ИНН 7801000005); ЗАО СаратоврегионстройС Инвест (ИНН 7000000127)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>СЗ Стройзаказчик, Республика Башкортостан</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>АО СЗ Стройзаказчик (ИНН 8000000025); ООО СЗ Стройзаказчик Трейд (ИНН 8000000025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Строительная компания Южный Город, Краснодарский край</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО Строительная компания Регион (ИНН 9000000645); ООО Строительная компания Сити (ИНН 9000000646)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>СК Алькасар, Пензенская область</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>АО СК Алькасар Строй (ИНН 1000001300); ООО СК Алькасар Девелопмент (ИНН 1000001301); ПАО СК Алькасар Инвест (ИНН 1000001302)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>СК ПАРТНЁР, Костромская область</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>ООО СК ПАРТНЁР (ИНН 2000001310), АО СК ПАРТНЁР Капитал (ИНН 2000001311)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>СЗ Символ плюс, Челябинская область</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>АО СЗ Символ (ИНН 3000000132)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>СБТ, г.Москва</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>АО Новый ЖБИ (ИНН 7701000001); ООО СБТ Сервис (ИНН 4000000133)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>СЗ Альфастройальянс, Республика Хакасия</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СЗ Альфастройальянс Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>СЗ Простор Девелопмент, Оренбургская область</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>АО СЗ Простор (ИНН 5000000405); ООО СЗ Простор Девелопмент (ИНН 5000000406), СЗ СЗ Простор Проект (ИНН 5000000407)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ГК ИСТОК, Красноярский край</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>АО ИСТОК Логистик (ИНН 6000001360); ООО ИСТОК Недвижимость (ИНН 6000001361); ПАО ИСТОК Риэлт (ИНН 6000001362); ЗАО ИСТОК Консалтинг (ИНН 6000001363)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ЕгорлыкАвто, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>АО ЕгорлыкАвто Риэлт (ИНН 5001000004); ООО ЕгорлыкАвто (ИНН 7801000005); ЗАО ЕгорлыкАвто Инвест (ИНН 7000000137)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>СЗ СтройИнвестПроект, Свердловская область</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>АО СЗ СтройИнвестПроект (ИНН 8000000027); ООО СЗ СтройИнвестПроект Трейд (ИНН 8000000027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ООО Пятачок, Курганская область</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО ООО Пятачок Регион (ИНН 9000000695); ООО ООО Пятачок Сити (ИНН 9000000696)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Промресурс-М, Республика Коми</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>АО Промресурс Строй (ИНН 1000001400); ООО Промресурс Девелопмент (ИНН 1000001401); ПАО Промресурс Инвест (ИНН 1000001402)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ТАГОРА, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ООО ТАГОРА (ИНН 2000001410), АО ТАГОРА Капитал (ИНН 2000001411)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ООО СтройИнвестИндустрия, Республика Карелия</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>АО ООО СтройИнвестИндустрия (ИНН 3000000142)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ГК Пересвет-Инвест, г.Москва</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>ООО ЖБИ-23 Трейд (ИНН 7701000001); ООО Пересвет Инвест Сервис (ИНН 4000000143)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>СЗ Паллада, Калининградская область</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СЗ Паллада Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>СЗ Дом-Инвест, Пензенская область</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>АО СЗ Дом (ИНН 5000000435); ООО СЗ Дом Девелопмент (ИНН 5000000436), СЗ СЗ Дом Проект (ИНН 5000000437)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>СЗ Инвестстрой, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>АО СЗ Инвестстрой Инвест (ИНН 6000001460); ООО СЗ Инвестстрой Холдинг (ИНН 6000001461); ПАО СЗ Инвестстрой Групп (ИНН 6000001462); ЗАО СЗ Инвестстрой Капитал (ИНН 6000001463)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ФЭСК МИГ, Ярославская область</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>АО ФЭСК МИГ Риэлт (ИНН 5001000004); ООО ФЭСК МИГ (ИНН 7801000005); ЗАО ФЭСК МИГ Инвест (ИНН 7000000147)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>М-Тастрой-19, Астраханская область</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>АО Тастрой 19 (ИНН 8000000029); ООО Тастрой 19 Трейд (ИНН 8000000029)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>ООО НВС, Республика Саха (Якутия)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО ООО НВС Регион (ИНН 9000000745); ООО ООО НВС Сити (ИНН 9000000746)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>СУ ДОРОЖНИК, Новосибирская область</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>АО СУ ДОРОЖНИК Строй (ИНН 1000001500); ООО СУ ДОРОЖНИК Девелопмент (ИНН 1000001501); ПАО СУ ДОРОЖНИК Инвест (ИНН 1000001502)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Эстейт Инвестментс, Московская область</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>ООО Эстейт Инвестментс (ИНН 2000001510), АО Эстейт Инвестментс Капитал (ИНН 2000001511)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Стройдом Развитие, Московская область</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>АО Стройдом Развитие (ИНН 3000000152)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>СЗ Лавр, Кемеровская область</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); ООО СЗ Лавр Сервис (ИНН 4000000153)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>CP Приватстрой, Амурская область</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО CP Приватстрой Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Федоровская служба благоустройства, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>АО Федоровская служба (ИНН 5000000465); ООО Федоровская служба Девелопмент (ИНН 5000000466), СЗ Федоровская служба Проект (ИНН 5000000467)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>ООО Трест-2, Новгородская область</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>АО ООО Трест Риэлт (ИНН 6000001560); ООО ООО Трест Консалтинг (ИНН 6000001561); ПАО ООО Трест Парк (ИНН 6000001562); ЗАО ООО Трест Центр (ИНН 6000001563)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Мастер, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>АО Мастер Риэлт (ИНН 5001000004); ООО Мастер (ИНН 7801000005); ЗАО Мастер Инвест (ИНН 7000000157)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Агрострой, Вологодская область</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>АО Агрострой (ИНН 8000000031); ООО Агрострой Трейд (ИНН 8000000031)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>СЗ АТЛАС, Республика Татарстан (Татарстан)</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО СЗ АТЛАС Регион (ИНН 9000000795); ООО СЗ АТЛАС Сити (ИНН 9000000796)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>СКВС, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>АО СКВС Строй (ИНН 1000001600); ООО СКВС Девелопмент (ИНН 1000001601); ПАО СКВС Инвест (ИНН 1000001602)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>СЗ Геанд, Калининградская область</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>ООО СЗ Геанд (ИНН 2000001610), АО СЗ Геанд Капитал (ИНН 2000001611)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>АКС, Красноярский край</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>АО АКС (ИНН 3000000162)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Технология и Селекция, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>АО Новый ЖБИ (ИНН 7701000001); ООО Технология Селекция Сервис (ИНН 4000000163)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>СМУ-3, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>АО ЗемПроектСтрой (ИНН 7701000002); ПАО СМУ Холдинг (ИНН 7701000003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Форум-М, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>АО Форум (ИНН 5000000495); ООО Форум Девелопмент (ИНН 5000000496), СЗ Форум Проект (ИНН 5000000497)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Арарат, Ростовская область</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>АО Арарат Групп (ИНН 6000001660); ООО Арарат Капитал (ИНН 6000001661); ПАО Арарат Проект (ИНН 6000001662); ЗАО Арарат ЖБИ (ИНН 6000001663)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>ДОМ-63, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>АО ДОМ 63 Риэлт (ИНН 5001000004); ООО ДОМ 63 (ИНН 7801000005); ЗАО ДОМ 63 Инвест (ИНН 7000000167)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>ДОРСТРОЙИНДУСТРИЯ, Саратовская область</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>АО ДОРСТРОЙИНДУСТРИЯ (ИНН 8000000033); ООО ДОРСТРОЙИНДУСТРИЯ Трейд (ИНН 8000000033)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>АН Терем, Костромская область</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>АО ЖБИ-23 (ИНН 7701000001); АО АН Терем Регион (ИНН 9000000845); ООО АН Терем Сити (ИНН 9000000846)</t>
         </is>
       </c>
     </row>
